--- a/data/UKMain.xlsx
+++ b/data/UKMain.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSD\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSDclaude\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0799336-A780-4F0E-83D7-480EB18E5D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC1BF21-8F61-4A12-9632-CD84FA5B4044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>t</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>CumPopShares</t>
+  </si>
+  <si>
+    <t>2026-10-23 (review response A2): calibration!D2 and calibrationUS!D2 are public cash spending on old-age and survivors pensions in 2020, 7.836% of GDP, OECD SOCX (OECD.ELS.SPD:DSD_SOCX_AGG, public ES10, old age and survivors TP01, in cash C, % of GDP; retrieved 2026-09-30), the value in data/oecdFigure1.csv column pensionSpending (figure 1.1), over the labour share 1-B2. They were =0.083/(1-B2), SOCX cash plus in kind (8.269).</t>
   </si>
 </sst>
 </file>
@@ -503,12 +506,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AA8116-F26D-48D0-B2CE-7FBA20E167F1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -980,8 +988,8 @@
         <v>0.3</v>
       </c>
       <c r="D2">
-        <f>0.083/(1-B2)</f>
-        <v>0.11857142857142859</v>
+        <f>0.07836/(1-B2)</f>
+        <v>0.11194285714285715</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1054,8 +1062,8 @@
         <v>0.3</v>
       </c>
       <c r="D2">
-        <f>0.083/(1-B2)</f>
-        <v>0.11857142857142859</v>
+        <f>0.07836/(1-B2)</f>
+        <v>0.11194285714285715</v>
       </c>
       <c r="E2">
         <v>0</v>

--- a/data/UKMain.xlsx
+++ b/data/UKMain.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSDclaude\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC1BF21-8F61-4A12-9632-CD84FA5B4044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7516E75-03E2-4E1C-8279-622A9B03F7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Readme" sheetId="4" r:id="rId1"/>
-    <sheet name="population" sheetId="1" r:id="rId2"/>
-    <sheet name="heterogeneity" sheetId="2" r:id="rId3"/>
-    <sheet name="heterogeneityUS" sheetId="5" r:id="rId4"/>
-    <sheet name="calibration" sheetId="3" r:id="rId5"/>
-    <sheet name="calibrationUS" sheetId="6" r:id="rId6"/>
+    <sheet name="population" sheetId="1" r:id="rId1"/>
+    <sheet name="heterogeneity" sheetId="2" r:id="rId2"/>
+    <sheet name="heterogeneityUS" sheetId="5" r:id="rId3"/>
+    <sheet name="calibration" sheetId="3" r:id="rId4"/>
+    <sheet name="calibrationUS" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>t</t>
   </si>
@@ -79,9 +78,6 @@
     <t>Worker-to-retiree</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Universal share</t>
   </si>
   <si>
@@ -101,9 +97,6 @@
   </si>
   <si>
     <t>CumPopShares</t>
-  </si>
-  <si>
-    <t>2026-10-23 (review response A2): calibration!D2 and calibrationUS!D2 are public cash spending on old-age and survivors pensions in 2020, 7.836% of GDP, OECD SOCX (OECD.ELS.SPD:DSD_SOCX_AGG, public ES10, old age and survivors TP01, in cash C, % of GDP; retrieved 2026-09-30), the value in data/oecdFigure1.csv column pensionSpending (figure 1.1), over the labour share 1-B2. They were =0.083/(1-B2), SOCX cash plus in kind (8.269).</t>
   </si>
 </sst>
 </file>
@@ -505,18 +498,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AA8116-F26D-48D0-B2CE-7FBA20E167F1}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B1461-40F3-4621-A383-5FE9A849ADE2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A2">
+        <f>A3-30</f>
+        <v>1960</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3.8333171341666956</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.0919194313105167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A3">
+        <f>A4-30</f>
+        <v>1990</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3.5524059364826606</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.0919194313105167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A4">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3.0010999238514255</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.1740347147676515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A5">
+        <f>A4+30</f>
+        <v>2050</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2.6876030916833722</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.1210481688022833</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A6">
+        <f t="shared" ref="A6:A7" si="0">A5+30</f>
+        <v>2080</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2.5949772808054159</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.0059806887999434</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>2110</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2.5949772808054159</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.0059806887999434</v>
       </c>
     </row>
   </sheetData>
@@ -525,117 +593,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B1461-40F3-4621-A383-5FE9A849ADE2}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE76B0EF-4908-4CB2-98A8-B49EE220FB32}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.40625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <f>A3-30</f>
-        <v>1960</v>
-      </c>
-      <c r="B2" s="3">
-        <v>3.8333171341666956</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1.0919194313105167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <f>A4-30</f>
-        <v>1990</v>
-      </c>
-      <c r="B3" s="4">
-        <v>3.5524059364826606</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.0919194313105167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3.0010999238514255</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.1740347147676515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <f>A4+30</f>
-        <v>2050</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2.6876030916833722</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.1210481688022833</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f t="shared" ref="A6:A7" si="0">A5+30</f>
-        <v>2080</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2.5949772808054159</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.0059806887999434</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>2110</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2.5949772808054159</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.0059806887999434</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE76B0EF-4908-4CB2-98A8-B49EE220FB32}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
@@ -653,10 +626,10 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -683,7 +656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -711,7 +684,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -739,7 +712,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -774,21 +747,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5E9FCF-7A05-4ACB-BAF0-46FE9604B76B}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
@@ -806,10 +779,10 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -833,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -866,7 +839,7 @@
         <v>58.451848885082313</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -899,7 +872,7 @@
         <v>50.750330874000596</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -930,6 +903,80 @@
       <c r="H5">
         <f>FORECAST($B5,heterogeneity!H$3:H$5,heterogeneity!$B$3:$B$5)</f>
         <v>40.143939414794481</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E48DC5-CA22-4A6E-BD10-69F2BD6158FF}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.40625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>0.3</v>
+      </c>
+      <c r="C2">
+        <v>0.3</v>
+      </c>
+      <c r="D2">
+        <f>0.07836/(1-B2)</f>
+        <v>0.11194285714285715</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>heterogeneity!H4/heterogeneity!H3</f>
+        <v>0.69405099150141647</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <f>SUMPRODUCT(heterogeneity!C3:C5,heterogeneity!D3:D5)/52</f>
+        <v>34.726807834290398</v>
       </c>
     </row>
   </sheetData>
@@ -938,20 +985,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E48DC5-CA22-4A6E-BD10-69F2BD6158FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932F6545-17FF-4258-AE10-01CCF196D739}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.40625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -965,19 +1012,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
       <c r="H1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -995,85 +1042,11 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <f>heterogeneity!H4/heterogeneity!H3</f>
-        <v>0.69405099150141647</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <f>SUMPRODUCT(heterogeneity!C3:C5,heterogeneity!D3:D5)/52</f>
-        <v>34.726807834290398</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932F6545-17FF-4258-AE10-01CCF196D739}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2020</v>
-      </c>
-      <c r="B2">
-        <v>0.3</v>
-      </c>
-      <c r="C2">
-        <v>0.3</v>
-      </c>
-      <c r="D2">
-        <f>0.07836/(1-B2)</f>
-        <v>0.11194285714285715</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
         <f>heterogeneityUS!H4/heterogeneityUS!H3</f>
         <v>0.86824166971650329</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <f>SUMPRODUCT(heterogeneityUS!C3:C5,heterogeneityUS!D3:D5)/52</f>
